--- a/sampleprojects/CorporateTax/excel/states/SD_corp.xlsx
+++ b/sampleprojects/CorporateTax/excel/states/SD_corp.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="91">
   <si>
     <t>DT: Determine SD Filing Requirement</t>
   </si>
@@ -52,7 +52,7 @@
     <t>General business corporation (not financial institution or insurance company)</t>
   </si>
   <si>
-    <t>result.sd_is_financial_institution == false AND result.sd_is_insurance_company == false</t>
+    <t>sd_result.is_financial_institution == false AND sd_result.is_insurance_company == false</t>
   </si>
   <si>
     <t>Y</t>
@@ -67,7 +67,7 @@
     <t>Financial institution subject to Bank Franchise Tax</t>
   </si>
   <si>
-    <t>result.sd_is_financial_institution == true</t>
+    <t>sd_result.is_financial_institution == true</t>
   </si>
   <si>
     <t>-</t>
@@ -76,7 +76,7 @@
     <t>Insurance company subject to Insurance Premium Tax</t>
   </si>
   <si>
-    <t>result.sd_is_insurance_company == true</t>
+    <t>sd_result.is_insurance_company == true</t>
   </si>
   <si>
     <t>ACTIONS: COMMENTS</t>
@@ -88,7 +88,7 @@
     <t>General corporation - no corporate income tax; South Dakota has NO corporate income tax for general corporations</t>
   </si>
   <si>
-    <t>set result.sd_no_corporate_tax = true; set apportionment.state_tax = 0.0; set apportionment.state_tax_rate = 0.0; set apportionment.state_refund_or_owed = apportionment.state_payments; add "South Dakota has NO corporate income tax. Any estimated payments are refunded. Reference: SD Constitution Article XI" to job.audit_trail;</t>
+    <t>set sd_result.no_corporate_tax = true; set apportionment.state_tax = 0.0; set sd_apportionment.state_tax_rate = 0.0; set apportionment.state_refund_or_owed = apportionment.state_payments; add "South Dakota has NO corporate income tax. Any estimated payments are refunded. Reference: SD Constitution Article XI" to job.audit_trail;</t>
   </si>
   <si>
     <t>X</t>
@@ -97,13 +97,13 @@
     <t>Financial institution - Bank Franchise Tax (NOT income tax); Financial institutions pay Bank Franchise Tax (separate from general corporate taxation)</t>
   </si>
   <si>
-    <t>set apportionment.state_tax = result.sd_bank_franchise_tax; set apportionment.state_tax_rate = 0.0; add "SD Bank Franchise Tax applies (NOT corporate income tax). Reference: SDCL 10-43" to job.audit_trail;</t>
+    <t>set apportionment.state_tax = sd_result.bank_franchise_tax; set sd_apportionment.state_tax_rate = 0.0; add "SD Bank Franchise Tax applies (NOT corporate income tax). Reference: SDCL 10-43" to job.audit_trail;</t>
   </si>
   <si>
     <t>Insurance company - Insurance Premium Tax (NOT income tax); Insurance companies pay Insurance Premium Tax (separate from general corporate taxation)</t>
   </si>
   <si>
-    <t>set apportionment.state_tax = result.sd_insurance_premium_tax; set apportionment.state_tax_rate = 0.0; add "SD Insurance Premium Tax applies (NOT corporate income tax). Reference: SDCL 10-44" to job.audit_trail;</t>
+    <t>set apportionment.state_tax = sd_result.insurance_premium_tax; set sd_apportionment.state_tax_rate = 0.0; add "SD Insurance Premium Tax applies (NOT corporate income tax). Reference: SDCL 10-44" to job.audit_trail;</t>
   </si>
   <si>
     <t>DT: Calculate SD Income Adjustments</t>
@@ -121,7 +121,7 @@
     <t>General corporation - no income tax adjustments; South Dakota has NO corporate income tax - no adjustments</t>
   </si>
   <si>
-    <t>set apportionment.state_tax_rate = 0.0; set apportionment.state_additions = 0.0; set apportionment.state_subtractions = 0.0; set apportionment.state_taxable_income = 0.0; add "SD has NO corporate income tax. No adjustments needed." to job.audit_trail;</t>
+    <t>set sd_apportionment.state_tax_rate = 0.0; set apportionment.state_additions = 0.0; set apportionment.state_subtractions = 0.0; set apportionment.state_taxable_income = 0.0; add "SD has NO corporate income tax. No adjustments needed." to job.audit_trail;</t>
   </si>
   <si>
     <t>Specialized entity - no income adjustments; Financial institution or insurance company - no income tax adjustments</t>
@@ -142,7 +142,7 @@
     <t>General corporation - $0 tax; South Dakota has NO corporate income tax</t>
   </si>
   <si>
-    <t>set apportionment.state_tax = 0.0; set apportionment.state_tax_rate = 0.0; set apportionment.state_refund_or_owed = apportionment.state_payments; set result.sd_no_corporate_tax = true; add "South Dakota Corporate Tax: $0. NO corporate income tax, NO franchise tax, NO gross receipts tax. Any estimated payments refunded." to job.audit_trail;</t>
+    <t>set apportionment.state_tax = 0.0; set sd_apportionment.state_tax_rate = 0.0; set apportionment.state_refund_or_owed = apportionment.state_payments; set sd_result.no_corporate_tax = true; add "South Dakota Corporate Tax: $0. NO corporate income tax, NO franchise tax, NO gross receipts tax. Any estimated payments refunded." to job.audit_trail;</t>
   </si>
   <si>
     <t>Specialized entity - tax already calculated; Financial institution or insurance company - tax calculated in table 54500</t>
@@ -193,10 +193,10 @@
     <t>Reference</t>
   </si>
   <si>
-    <t>apportionment</t>
-  </si>
-  <si>
-    <t>(8 attributes)</t>
+    <t>sd_apportionment</t>
+  </si>
+  <si>
+    <t>(4 attributes)</t>
   </si>
   <si>
     <t>apportionment_formula</t>
@@ -226,33 +226,12 @@
     <t>SD economic nexus for SALES TAX: $100,000 in sales (Wayfair standard)</t>
   </si>
   <si>
-    <t>state_additions</t>
+    <t>state_tax_rate</t>
   </si>
   <si>
     <t>0.0</t>
   </si>
   <si>
-    <t>state_code</t>
-  </si>
-  <si>
-    <t>SD</t>
-  </si>
-  <si>
-    <t>South Dakota state code</t>
-  </si>
-  <si>
-    <t>state_credits</t>
-  </si>
-  <si>
-    <t>Not applicable - South Dakota has no corporate income tax or credits</t>
-  </si>
-  <si>
-    <t>state_subtractions</t>
-  </si>
-  <si>
-    <t>state_tax_rate</t>
-  </si>
-  <si>
     <t>South Dakota has NO corporate income tax - rate is 0.0%</t>
   </si>
   <si>
@@ -268,25 +247,25 @@
     <t>SD economic nexus for SALES TAX: 200 or more transactions</t>
   </si>
   <si>
-    <t>result</t>
+    <t>sd_result</t>
   </si>
   <si>
     <t>(5 attributes)</t>
   </si>
   <si>
-    <t>sd_bank_franchise_tax</t>
+    <t>bank_franchise_tax</t>
   </si>
   <si>
     <t>SD Bank Franchise Tax (ONLY for banks/financial institutions, NOT general corporations)</t>
   </si>
   <si>
-    <t>sd_insurance_premium_tax</t>
+    <t>insurance_premium_tax</t>
   </si>
   <si>
     <t>SD Insurance Premium Tax (ONLY for insurance companies, NOT general corporations)</t>
   </si>
   <si>
-    <t>sd_is_financial_institution</t>
+    <t>is_financial_institution</t>
   </si>
   <si>
     <t>boolean</t>
@@ -298,13 +277,13 @@
     <t>Is financial institution subject to SD Bank Franchise Tax (NOT general corporations)</t>
   </si>
   <si>
-    <t>sd_is_insurance_company</t>
+    <t>is_insurance_company</t>
   </si>
   <si>
     <t>Is insurance company subject to SD Insurance Premium Tax (NOT general corporations)</t>
   </si>
   <si>
-    <t>sd_no_corporate_tax</t>
+    <t>no_corporate_tax</t>
   </si>
   <si>
     <t>true</t>
@@ -2494,7 +2473,7 @@
         <v>63</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>14</v>
@@ -2517,16 +2496,16 @@
         <v>14</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>61</v>
+        <v>72</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>73</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>14</v>
@@ -2535,7 +2514,7 @@
         <v>63</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>14</v>
@@ -2554,203 +2533,203 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="H8" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="A8" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="8" t="s">
+      <c r="D9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="F9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="8" t="s">
+      <c r="F9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>63</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M9" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M9" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="8" t="s">
         <v>14</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="7" t="s">
+      <c r="D10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="F10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" s="7" t="s">
+      <c r="F10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="8" t="s">
         <v>63</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M10" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M10" s="8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>14</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="7" t="s">
         <v>63</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M11" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M11" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="D12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
+      <c r="F12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H12" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M12" s="8" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="s">
         <v>14</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>66</v>
+        <v>88</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>83</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>14</v>
@@ -2759,7 +2738,7 @@
         <v>63</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="I13" s="7" t="s">
         <v>14</v>
@@ -2774,170 +2753,6 @@
         <v>14</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="H14" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M14" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="H15" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M15" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="H16" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K16" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L16" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M16" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="H17" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J17" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K17" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L17" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M17" s="7" t="s">
         <v>14</v>
       </c>
     </row>
